--- a/data/trans_orig/P36BPD06_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD06_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de raciones de mantequilla, margarina o nata que consume al día en 2023</t>
+          <t>Población según el número de raciones de mantequilla, margarina o nata que consume al día en 2023 (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>93834</t>
+          <t>94790</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>131200</t>
+          <t>134099</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>104369</t>
+          <t>104362</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>138070</t>
+          <t>137306</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>208452</t>
+          <t>209942</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>259434</t>
+          <t>258950</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,82%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>500172</t>
+          <t>497273</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>537538</t>
+          <t>536582</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>537300</t>
+          <t>538064</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>571001</t>
+          <t>571008</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1047308</t>
+          <t>1047792</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1098290</t>
+          <t>1096800</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>83,93%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>135814</t>
+          <t>119836</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>332424</t>
+          <t>329052</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>217342</t>
+          <t>220195</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>262803</t>
+          <t>263509</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>331936</t>
+          <t>294986</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>573982</t>
+          <t>571127</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,63%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>856369</t>
+          <t>859741</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1052979</t>
+          <t>1068957</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>692905</t>
+          <t>692199</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>738366</t>
+          <t>735513</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1570519</t>
+          <t>1573374</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1812565</t>
+          <t>1849515</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>86,24%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>113992</t>
+          <t>116921</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>163844</t>
+          <t>162690</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>176888</t>
+          <t>176293</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>600460</t>
+          <t>626193</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>312666</t>
+          <t>313258</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>865921</t>
+          <t>878540</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>53,68%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>539561</t>
+          <t>540715</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>589413</t>
+          <t>586484</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>332906</t>
+          <t>307173</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>756478</t>
+          <t>757073</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>770850</t>
+          <t>758231</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1324105</t>
+          <t>1323513</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>80,86%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>212248</t>
+          <t>212996</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>268465</t>
+          <t>268936</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>296977</t>
+          <t>293680</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>538167</t>
+          <t>491706</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>525785</t>
+          <t>528059</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>786665</t>
+          <t>771955</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>38,32%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>653355</t>
+          <t>652884</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>709572</t>
+          <t>708824</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>554452</t>
+          <t>600913</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>795642</t>
+          <t>798939</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1227774</t>
+          <t>1242484</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1488654</t>
+          <t>1486380</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>61,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>73,79%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>580597</t>
+          <t>582424</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>824014</t>
+          <t>821203</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>879135</t>
+          <t>866545</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1570904</t>
+          <t>1559226</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1562250</t>
+          <t>1589899</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2291013</t>
+          <t>2362623</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>33,26%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2621376</t>
+          <t>2624187</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2864793</t>
+          <t>2862966</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2086159</t>
+          <t>2097837</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2777928</t>
+          <t>2790518</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4811440</t>
+          <t>4739830</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5540203</t>
+          <t>5512554</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>77,61%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD06_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD06_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>112384</t>
+          <t>129624</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>94790</t>
+          <t>109407</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>134099</t>
+          <t>151344</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>119999</t>
+          <t>135625</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>104362</t>
+          <t>118348</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>137306</t>
+          <t>153800</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>232383</t>
+          <t>265249</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>209942</t>
+          <t>239857</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>258950</t>
+          <t>294183</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,73%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>518988</t>
+          <t>556862</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>497273</t>
+          <t>535142</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>536582</t>
+          <t>577079</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>555371</t>
+          <t>597097</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>538064</t>
+          <t>578922</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>571008</t>
+          <t>614374</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1074359</t>
+          <t>1153959</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1047792</t>
+          <t>1125025</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1096800</t>
+          <t>1179351</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>83,1%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>631372</t>
+          <t>686486</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>631372</t>
+          <t>686486</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>631372</t>
+          <t>686486</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1306742</t>
+          <t>1419208</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1306742</t>
+          <t>1419208</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1306742</t>
+          <t>1419208</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>251136</t>
+          <t>278836</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>119836</t>
+          <t>246507</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>329052</t>
+          <t>309704</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>241189</t>
+          <t>275513</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>220195</t>
+          <t>248160</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>263509</t>
+          <t>299839</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>492325</t>
+          <t>554349</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>294986</t>
+          <t>510617</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>571127</t>
+          <t>594027</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>28,12%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>937657</t>
+          <t>765813</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>859741</t>
+          <t>734945</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1068957</t>
+          <t>798142</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>714519</t>
+          <t>792234</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>692199</t>
+          <t>767908</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>735513</t>
+          <t>819587</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1652176</t>
+          <t>1558047</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1573374</t>
+          <t>1518369</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1849515</t>
+          <t>1601779</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>75,83%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1188793</t>
+          <t>1044649</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1188793</t>
+          <t>1044649</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1188793</t>
+          <t>1044649</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>955708</t>
+          <t>1067747</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>955708</t>
+          <t>1067747</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>955708</t>
+          <t>1067747</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2144501</t>
+          <t>2112396</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2144501</t>
+          <t>2112396</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2144501</t>
+          <t>2112396</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>137482</t>
+          <t>168143</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>116921</t>
+          <t>140629</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>162690</t>
+          <t>195200</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>351057</t>
+          <t>173825</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>176293</t>
+          <t>152700</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>626193</t>
+          <t>195931</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>488538</t>
+          <t>341968</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>313258</t>
+          <t>309707</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>878540</t>
+          <t>377457</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>23,39%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>565923</t>
+          <t>633644</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>540715</t>
+          <t>606587</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>586484</t>
+          <t>661158</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>582309</t>
+          <t>638434</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>307173</t>
+          <t>616328</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>757073</t>
+          <t>659559</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1148233</t>
+          <t>1272077</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>758231</t>
+          <t>1236588</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1323513</t>
+          <t>1304338</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>80,81%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>703405</t>
+          <t>801787</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>703405</t>
+          <t>801787</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>703405</t>
+          <t>801787</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1636771</t>
+          <t>1614045</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1636771</t>
+          <t>1614045</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1636771</t>
+          <t>1614045</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>239604</t>
+          <t>268589</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>212996</t>
+          <t>236796</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>268936</t>
+          <t>299099</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>353759</t>
+          <t>324519</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>293680</t>
+          <t>297246</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>491706</t>
+          <t>353603</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>593364</t>
+          <t>593108</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>528059</t>
+          <t>546430</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>771955</t>
+          <t>636412</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>30,3%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>682216</t>
+          <t>715308</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>652884</t>
+          <t>684798</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>708824</t>
+          <t>747101</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>738860</t>
+          <t>791669</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>600913</t>
+          <t>762585</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>798939</t>
+          <t>818942</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1421075</t>
+          <t>1506977</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1242484</t>
+          <t>1463673</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1486380</t>
+          <t>1553655</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>73,98%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>921820</t>
+          <t>983897</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>921820</t>
+          <t>983897</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>921820</t>
+          <t>983897</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1092619</t>
+          <t>1116188</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1092619</t>
+          <t>1116188</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1092619</t>
+          <t>1116188</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2014439</t>
+          <t>2100085</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2014439</t>
+          <t>2100085</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2014439</t>
+          <t>2100085</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>740606</t>
+          <t>845192</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>582424</t>
+          <t>787103</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>821203</t>
+          <t>901671</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1066004</t>
+          <t>909481</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>866545</t>
+          <t>866526</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1559226</t>
+          <t>957580</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1806611</t>
+          <t>1754674</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1589899</t>
+          <t>1681482</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2362623</t>
+          <t>1829631</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>25,25%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2704784</t>
+          <t>2671626</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2624187</t>
+          <t>2615147</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2862966</t>
+          <t>2729715</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2591059</t>
+          <t>2819434</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2097837</t>
+          <t>2771335</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2790518</t>
+          <t>2862389</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5295842</t>
+          <t>5491060</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4739830</t>
+          <t>5416103</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5512554</t>
+          <t>5564252</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>76,79%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3445390</t>
+          <t>3516818</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3445390</t>
+          <t>3516818</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3445390</t>
+          <t>3516818</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3657063</t>
+          <t>3728915</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3657063</t>
+          <t>3728915</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3657063</t>
+          <t>3728915</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7102453</t>
+          <t>7245734</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7102453</t>
+          <t>7245734</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7102453</t>
+          <t>7245734</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
